--- a/results/b200_dsr_fp4/b200_dsr_fp4_mtp0_ep1_tp4_sglang059_profiling/b200_vs_mi355x_kernel_map_c64_ep1.xlsx
+++ b/results/b200_dsr_fp4/b200_dsr_fp4_mtp0_ep1_tp4_sglang059_profiling/b200_vs_mi355x_kernel_map_c64_ep1.xlsx
@@ -414,18 +414,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -436,40 +440,60 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>B200_Module</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>B200_Operator</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>B200_Kernel</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>B200_Stream</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>B200_us</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>B200_Overlap_us</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>B200_Overlap_With</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>MI355X_Module</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>MI355X_Kernel</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>MI355X_us</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -486,33 +510,49 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EP_AR+residual+RMSNorm(fused)</t>
+          <t>comm_norm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>lamport_AR+RMSNorm #1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>allreduce_fusion_kernel_oneshot_lamport</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>13</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>23</v>
+      </c>
+      <c r="G2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>qkv_a_proj_GEMM(pdl):11.7us</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>input_layernorm</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>reduce_scatter_cross_device_store</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>B200 fuses AR+residual+RMSNorm; *estimated from 23.5/2</t>
+      <c r="L2" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>B200 fuses AR+res+RMSNorm</t>
         </is>
       </c>
     </row>
@@ -520,24 +560,32 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EP_AR</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>input_layernorm</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>local_device_load_rmsnorm</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="L3" t="n">
         <v>4.7</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>MI355X only (comm+norm split)</t>
         </is>
@@ -547,26 +595,34 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EP_AR</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
         <is>
           <t>input_layernorm</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>dynamic_per_token_scaled_quant&lt;32&gt;</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="L4" t="n">
         <v>4.3</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>MI355X only (FP8 input quant)</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>MI355X only (FP8 input quant for qkv_a)</t>
         </is>
       </c>
     </row>
@@ -576,36 +632,52 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>MHA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>qkv_proj</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>qkv_a_proj_GEMM</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>nvjet_splitK_TNT</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="n">
+        <v>23</v>
+      </c>
+      <c r="G5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>EP_AR(pdl):11.7us | splitK_reduce(pdl):1.5us</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>gemm_a8w8</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>kernel_gemm_xdl_cshuffle_v3_multi_d_b_preshuffle (128x16x32)</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="L5" t="n">
         <v>11.1</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>B200 FP4 splitK; MI355X FP8 preshuffle</t>
         </is>
@@ -617,28 +689,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>MHA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>qkv_proj</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>qkv_a_splitK_reduce</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>splitKreduce_kernel</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>23</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>B200 only</t>
+          <t>qkv_a_proj(pdl):1.5us | q/k_norm(pdl):1.1us</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>B200 only (splitK reduction)</t>
         </is>
       </c>
     </row>
@@ -648,36 +736,52 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>MHA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q/k_norm_RMSNorm x2</t>
+          <t>qkv_proj</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>q/k_norm_RMSNorm #1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>RMSNormKernel</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="n">
+        <v>23</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>q/k_norm#2(dual_stream):1.6us | splitK_reduce(pdl):1.1us</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>q_proj_and_k_up_proj</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>fused_qk_rmsnorm_group_quant_kernel</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="L7" t="n">
         <v>4.2</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>MI355X fuses both norms into 1 kernel</t>
         </is>
@@ -689,36 +793,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>MHA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q_b_proj_GEMM</t>
+          <t>qkv_proj</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>nvjet_v_bz_TNN</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>gemm_a8w8</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>kernel_gemm_xdl_cshuffle_v3_multi_d_b_preshuffle (256x32x64)</t>
-        </is>
+          <t>q/k_norm_RMSNorm #2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RMSNormKernel</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>385</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.3</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>1.6</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>q/k_norm#1(dual_stream):1.6us</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>B200 second norm (dual stream)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -726,36 +840,52 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>MHA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>uk_gemm(K_expansion)</t>
+          <t>qkv_proj</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>nvjet_v_bz_TNT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>batched_gemm</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>batched_gemm_a8w8_M32_N128_K128</t>
-        </is>
+          <t>q_b_proj_GEMM</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>nvjet_v_bz_TNN</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>23</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.3</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>uk_gemm(pdl):1.3us</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>gemm_a8w8</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>kernel_gemm_xdl_cshuffle_v3_multi_d_b_preshuffle (256x16x64)</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -763,36 +893,52 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>MHA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RoPE+KV_cache_write</t>
+          <t>qkv_proj</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RopeQuantizeKernel</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>rope_and_kv_cache</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>fuse_qk_rope_concat_and_cache_mla_per_head_kernel</t>
-        </is>
+          <t>uk_gemm (K_expansion)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>nvjet_v_bz_TNT</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>23</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.4</v>
       </c>
       <c r="H10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>q_b_proj(pdl):1.3us</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>batched_gemm</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>batched_gemm_a8w8_M32_N128_K128</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -800,30 +946,48 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>MHA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>set_mla_kv</t>
+          <t>rope_attn</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>set_mla_kv_buffer_kernel</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>B200 only</t>
-        </is>
-      </c>
+          <t>RoPE+KV_cache_write</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RopeQuantizeKernel</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>23</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>rope_and_kv_cache</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fuse_qk_rope_concat_and_cache_mla_per_head_kernel</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -831,63 +995,91 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>MHA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Attention(FMHA)</t>
+          <t>rope_attn</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>fmhaSm100fKernel</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>mla_decode</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>mla_a8w8_qh16_qseqlen1_gqaratio16_ps</t>
-        </is>
+          <t>set_mla_kv</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>set_mla_kv_buffer_kernel</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.7</v>
       </c>
       <c r="H12" t="n">
-        <v>26.4</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>B200 only</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MHA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>rope_attn</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Attention (FMHA)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>fmhaSm100fKernel</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>23</v>
+      </c>
+      <c r="G13" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
         <is>
           <t>mla_decode</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>kn_mla_reduce_v1_ps&lt;512,16,1&gt;</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>MI355X only (MLA reduce)</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>mla_a8w8_qh16_qseqlen1_gqaratio16_ps</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -895,32 +1087,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Proj</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>o_proj_quant(BF16-&gt;FP4)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>cvt_fp16_to_fp4</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>2.2</v>
-      </c>
+          <t>MHA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>dynamic_per_token_scaled_quant&lt;16&gt;</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mla_decode</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>kn_mla_reduce_v1_ps&lt;512,16,1&gt;</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>MI355X only (MLA reduce)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -928,36 +1122,48 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Proj</t>
+          <t>MHA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>uv_gemm(V_expansion)</t>
+          <t>out_proj</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>uv_gemm (V_expansion)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>nvjet_h_bz_TNT</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
+        <v>23</v>
+      </c>
+      <c r="G15" t="n">
         <v>4</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
         <is>
           <t>v_up_proj_and_o_proj</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>batched_gemm_a8w8_M32_N64_K128</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -965,38 +1171,46 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Proj</t>
+          <t>O_proj</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>o_proj_GEMM</t>
+          <t>out_proj</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DeviceGemmFp4GemmSm100 (256x256)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>v_up_proj_and_o_proj</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>FlatmmKernel (FlyDSL cktile)</t>
-        </is>
+          <t>o_proj_quant (BF16-&gt;FP4)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>cvt_fp16_to_fp4</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>23</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.2</v>
       </c>
       <c r="H16" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>B200 FP4 Cutlass; MI355X FP8 FlatMM</t>
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>dynamic_per_token_scaled_quant&lt;16&gt;</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>B200 FP4 quant; MI355X FP8 quant</t>
         </is>
       </c>
     </row>
@@ -1006,38 +1220,50 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EP_AR</t>
+          <t>O_proj</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EP_AR+residual+RMSNorm(fused) #2</t>
+          <t>out_proj</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>allreduce_fusion_kernel_oneshot_lamport</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>post_attn_layernorm</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>reduce_scatter_cross_device_store</t>
-        </is>
+          <t>o_proj_GEMM</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>DeviceGemmFp4GemmSm100</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>23</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11.1</v>
       </c>
       <c r="H17" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>*estimated from 23.5/2</t>
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>v_up_proj_and_o_proj</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>FlatmmKernel (FlyDSL cktile)</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>B200 FP4 Cutlass; MI355X FP8 FlatMM</t>
         </is>
       </c>
     </row>
@@ -1045,49 +1271,87 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EP_AR</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>comm_norm</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>lamport_AR+RMSNorm #2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>allreduce_fusion_kernel_oneshot_lamport</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>23</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>router_GEMM(dual_stream):8.6us</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>post_attn_layernorm</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>local_device_load_rmsnorm</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>MI355X only</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>reduce_scatter_cross_device_store</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EP_AR</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>triton_poi_fused_as_strided_clone x3</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>MI355X only (tensor reshape)</t>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>post_attn_layernorm</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>local_device_load_rmsnorm</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>MI355X only</t>
         </is>
       </c>
     </row>
@@ -1097,38 +1361,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MoE_Route</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>shared_expert(FP4 GEMMs+SiLU)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>DeviceGemmFp4 x2 + SiLU + cvt x2</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>29</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>gemm_a16w16</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>bf16gemm_fp32bf16_tn_64x64_splitk_clean</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>B200 shared expert parallel w/ MoE; MI355X router GEMM</t>
+          <t>EP_AR</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>triton_poi_fused_as_strided_clone_1</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>MI355X only (tensor reshape #1)</t>
         </is>
       </c>
     </row>
@@ -1138,36 +1392,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MoE_Route</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>router_GEMM</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>nvjet_h_bz_splitK_TNT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>mxfp4_moe</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>grouped_topk_opt_sort_kernel</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>4.2</v>
-      </c>
+          <t>EP_AR</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>triton_poi_fused_as_strided_clone_2</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>MI355X only (tensor reshape #2)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1175,36 +1423,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MoE_Route</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>router_splitK_reduce</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>splitKreduce_kernel</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>mxfp4_moe</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>MoeSortingMultiPhaseKernel_P0_v2 + P23</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>8.699999999999999</v>
-      </c>
+          <t>EP_AR</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>triton_poi_fused_as_strided_clone_copy__0</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>MI355X only (tensor reshape #3)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1217,31 +1459,51 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TopK_select</t>
+          <t>router</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>routingMainKernel</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>mxfp4_moe</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>mxfp4_quant_moe_sort_kernel&lt;256&gt;</t>
-        </is>
+          <t>router_GEMM</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>nvjet_h_bz_splitK_TNT</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>385</v>
+      </c>
+      <c r="G23" t="n">
+        <v>12.9</v>
       </c>
       <c r="H23" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>12.1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>EP_AR(dual_stream):8.6us | shared_quant(dual_stream):2.5us | splitK_reduce(pdl):1.4us | shared_GEMM(dual_stream):1.1us</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>gemm_a16w16</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>bf16gemm_fp32bf16_tn_64x64_splitk_clean</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>MI355X router GEMM</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1249,36 +1511,52 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MoE_Route</t>
+          <t>Shared_Exp</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>expert_sort</t>
+          <t>shared_expert</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>routingIndicesClusterKernel</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F24" t="inlineStr">
+          <t>shared_quant #1 (BF16-&gt;FP4)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>cvt_fp16_to_fp4</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>23</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>router_GEMM(dual_stream):2.5us</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>mxfp4_moe</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>mxfp4_quant_moe_sort_kernel&lt;8&gt;</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>mxfp4_quant_moe_sort_kernel&lt;256&gt;</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1286,28 +1564,44 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MoE_Expert</t>
+          <t>Shared_Exp</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MoE_input_quant(BF16-&gt;FP4)</t>
+          <t>shared_expert</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>quantize_with_block_size</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+          <t>shared_GEMM #1 (FP4)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>DeviceGemmFp4GemmSm100</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>23</v>
+      </c>
+      <c r="G25" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>16.2</v>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>B200 only: FP4 quant for MoE input</t>
+          <t>MoE_input_quant(dual_stream):3.7us | tensor_copy(dual_stream):3.5us | TopK_select(dual_stream):3.2us | splitK_reduce(dual_stream):3.1us | expert_sort(dual_stream):2.8us | router_GEMM(dual_stream):1.1us</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Long GEMM overlaps with entire MoE routing on stream 385</t>
         </is>
       </c>
     </row>
@@ -1317,28 +1611,44 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MoE_Expert</t>
+          <t>MoE_Route</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>tensor_copy</t>
+          <t>router</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>unrolled_elementwise_kernel</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+          <t>router_splitK_reduce</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>splitKreduce_kernel</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>385</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.3</v>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>B200 only</t>
+          <t>shared_GEMM(dual_stream):3.1us | router_GEMM(pdl):1.4us | MoE_input_quant(pdl):1.3us</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>B200 only (splitK reduction)</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1658,44 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MoE_Expert</t>
+          <t>MoE_Route</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>gate_up_GEMM(+SwiGLU)</t>
+          <t>moe_expert</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>bmm_E2m1_E2m1E2m1</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>101.7</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>mxfp4_moe</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>kernel_moe_mxgemm_2lds&lt;MulABScaleShuffled&gt; (CK)</t>
-        </is>
+          <t>MoE_input_quant (BF16-&gt;FP4)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>quantize_with_block_size</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>385</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.7</v>
       </c>
       <c r="H27" t="n">
-        <v>102.1</v>
+        <v>3.7</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>EP1: FlyDSL tune match (expert=257,topk=9)</t>
+          <t>shared_GEMM(dual_stream):3.7us | splitK_reduce(pdl):1.3us</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>B200 only: FP4 quant for MoE input</t>
         </is>
       </c>
     </row>
@@ -1389,36 +1705,46 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MoE_Expert</t>
+          <t>MoE_Route</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>down_GEMM</t>
+          <t>residual_mem</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>bmm_Bfloat16_E2m1E2m1</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>mxfp4_moe</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>kernel_moe_mxgemm_2lds&lt;MulABScaleExpertWeight&gt; (CK)</t>
-        </is>
+          <t>tensor_copy</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>unrolled_elementwise_kernel</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>385</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.5</v>
       </c>
       <c r="H28" t="n">
-        <v>57</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>shared_GEMM(dual_stream):3.5us</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>B200 only</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1426,30 +1752,52 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MoE_Expert</t>
+          <t>MoE_Route</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MoE_finalize+residual</t>
+          <t>router</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>finalizeKernelVecLoad</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+          <t>TopK_select</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>routingMainKernel</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>385</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4.2</v>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>B200 only</t>
-        </is>
-      </c>
+          <t>shared_GEMM(dual_stream):3.2us | expert_sort(pdl):2.4us | SiLU_Mul(dual_stream):1.8us</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mxfp4_moe</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>grouped_topk_opt_sort_kernel</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1457,80 +1805,500 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Residual</t>
+          <t>Shared_Exp</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>residual_add</t>
+          <t>shared_expert</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>vectorized_elementwise_kernel</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+          <t>SiLU x Mul</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>act_and_mul_kernel</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>23</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.9</v>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>B200 only</t>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
+          <t>expert_sort(dual_stream):2.8us | TopK_select(dual_stream):1.8us</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>mxfp4_moe</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>mxfp4_quant_moe_sort_kernel&lt;64&gt;</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>MI355X quant between gate_up and down</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MoE_Route</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>expert_sort</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>routingIndicesClusterKernel</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>385</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>SiLU_Mul(dual_stream):2.8us | shared_GEMM(dual_stream):2.6us | TopK_select(pdl):2.4us | shared_quant(dual_stream):1.0us | gate_up(pdl):0.3us</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>mxfp4_moe</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>MoeSortingMultiPhaseKernel_P0_v2</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>MI355X expert sort phase 0</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MoE_Route</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>B200 kernel_sum: 346.1</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>MI355X TOTAL: 334.9</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>mxfp4_moe</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>MoeSortingMultiPhaseKernel_P23</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>MI355X expert sort phase 2-3</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Shared_Exp</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>shared_expert</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>shared_quant #2 (BF16-&gt;FP4)</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>B200 walltime: 285.9</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+          <t>cvt_fp16_to_fp4</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>23</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>gate_up(dual_stream):1.4us | expert_sort(dual_stream):1.0us</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MoE_Expert</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>moe_expert</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>gate_up_GEMM (+SwiGLU)</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>B200 overlap: 60.1</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+          <t>bmm_E2m1_E2m1E2m1</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>385</v>
+      </c>
+      <c r="G34" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>shared_GEMM(dual_stream):2.8us | shared_quant(dual_stream):1.4us | down_GEMM(pdl):0.4us | expert_sort(pdl):0.3us</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mxfp4_moe</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>moe_gemm1_0 (CK moe_mxgemm_2lds)</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>EP1: tune match (expert=257,topk=9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Shared_Exp</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>shared_expert</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>shared_GEMM #2 (FP4)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DeviceGemmFp4GemmSm100</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>23</v>
+      </c>
+      <c r="G35" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>down_GEMM(dual_stream):9.8us | gate_up(dual_stream):3.1us</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Runs during gate_up+down on stream 385</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MoE_Expert</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>moe_expert</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>down_GEMM</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>bmm_Bfloat16_E2m1E2m1</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>385</v>
+      </c>
+      <c r="G36" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>shared_GEMM(dual_stream):9.8us | MoE_finalize(pdl):0.5us | gate_up(pdl):0.4us</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>mxfp4_moe</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>moe_gemm2_0 (CK moe_mxgemm_2lds)</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>57</v>
+      </c>
+      <c r="M36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MoE_Expert</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>moe_expert</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MoE_finalize+residual</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>finalizeKernelVecLoad</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>385</v>
+      </c>
+      <c r="G37" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>down_GEMM(pdl):0.5us</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>B200 only</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Residual</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>residual_mem</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>residual_add</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>vectorized_elementwise_kernel</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>23</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>B200 only</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>B200 kernel_sum: 346.2</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>MI355X TOTAL: 334.6</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>B200 walltime: 285.3</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>B200 overlap: 61.6 (17.7%)</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1543,15 +2311,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1593,13 +2361,15 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
-      </c>
-      <c r="C2" t="n">
-        <v>13</v>
+        <v>13.5</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>~14</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>23.1</v>
+        <v>23.15</v>
       </c>
       <c r="E2" t="n">
         <v>37.9</v>
@@ -1613,24 +2383,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MHA (qkv-&gt;uv)</t>
+          <t>MHA (qkv-&gt;FMHA+uv_gemm)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="C3" t="n">
-        <v>59</v>
+        <v>68.40000000000001</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>~63</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>73.5</v>
+        <v>63.4</v>
       </c>
       <c r="E3" t="n">
         <v>68.7</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+7%</t>
+          <t>-8%</t>
         </is>
       </c>
     </row>
@@ -1641,20 +2413,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="C4" t="n">
-        <v>17</v>
+        <v>13.3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>~13</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>20.4</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="n">
         <v>15.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+32%</t>
+          <t>+39%</t>
         </is>
       </c>
     </row>
@@ -1665,13 +2439,15 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="C5" t="n">
-        <v>10</v>
+        <v>10.4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>~10</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>32.3</v>
+        <v>32.35</v>
       </c>
       <c r="E5" t="n">
         <v>17.5</v>
@@ -1685,72 +2461,158 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MOE (router-&gt;finalize)</t>
+          <t>Shared Expert</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>234.5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>182</v>
+        <v>31.3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>~22</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>185.6</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="n">
-        <v>219.8</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>B200 main stream; interleaved with MoE routing</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Residual</t>
+          <t>MoE Routing</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
+        <v>33.5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>~17</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>21.8</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>34.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-37%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>MoE Expert</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>346.1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>285.9</v>
+        <v>173.7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>~173</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>334.9</v>
+        <v>159.1</v>
       </c>
       <c r="E8" t="n">
+        <v>219.8</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Residual</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>~2</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>B200 only</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SUM (kernel)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>346.2</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>334.6</v>
+      </c>
+      <c r="E10" t="n">
         <v>363.8</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>-8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>B200 walltime</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>285.3</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B200 overlap</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>17.7%</t>
         </is>
       </c>
     </row>
